--- a/analysis/SPOT_Print_WhatIf_Scenarios.xlsx
+++ b/analysis/SPOT_Print_WhatIf_Scenarios.xlsx
@@ -56,7 +56,7 @@
       <color rgb="001F4E78"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,11 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CFE2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,7 +122,6 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -357,144 +351,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Print + Cut + Finishing — Avg vs Median Variance % by Qty Band</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Current (v3 Corrected Baseline)'!C14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Current (v3 Corrected Baseline)'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Current (v3 Corrected Baseline)'!$C$15:$C$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Current (v3 Corrected Baseline)'!D14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Current (v3 Corrected Baseline)'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Current (v3 Corrected Baseline)'!$D$15:$D$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Qty Band</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="1"/>
-          <min val="-0.4"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Variance %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Print + Cut — Avg vs Median Variance % by Qty Band</a:t>
             </a:r>
           </a:p>
@@ -621,145 +477,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Print + Cut + Finishing — Avg vs Median Variance % by Qty Band</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Scenario A'!C14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario A'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario A'!$C$15:$C$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Scenario A'!D14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario A'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario A'!$D$15:$D$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Qty Band</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="1"/>
-          <min val="-0.4"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Variance %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -897,145 +615,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Print + Cut + Finishing — Avg vs Median Variance % by Qty Band</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Scenario B'!C14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario B'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario B'!$C$15:$C$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Scenario B'!D14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario B'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario B'!$D$15:$D$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Qty Band</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="1"/>
-          <min val="-0.4"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Variance %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1173,144 +753,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Print + Cut + Finishing — Avg vs Median Variance % by Qty Band</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Scenario C'!C14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario C'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario C'!$C$15:$C$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Scenario C'!D14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenario C'!$A$15:$A$19</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenario C'!$D$15:$D$19</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Qty Band</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="1"/>
-          <min val="-0.4"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Variance %</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1330,28 +772,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1384,28 +804,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1433,28 +831,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1477,28 +853,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1796,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1975,570 +1329,300 @@
         <v>0.06808797794832507</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1-49</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>42</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.2824245128794613</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.1541820615915152</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.09006083594754205</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>0.02593961030356908</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>200-999</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>44</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0.1344094722554383</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.02096852502989452</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>-0.03575194858287743</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-0.0924724221956493</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>AVG Variance % — Print jobs by qty band</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>0.007048749911299275</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Qty Band</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>10% cut</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>15% cut</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>20% cut</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5000+</t>
+          <t>Print + Cut</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1-49</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>-0.2663159846685904</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>-0.2663159846685904</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>-0.2663159846685904</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>-0.2663159846685904</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.4749137041618482</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.3274223337456634</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.253676648537571</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.1799309633294786</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Print + Cut</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50-199</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.1562566818722815</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.1562566818722815</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1562566818722815</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1562566818722815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Print + Cut</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>200-999</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>55</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.2090815015308145</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0.08817335137773306</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.02771927630119228</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>-0.03273479877534836</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>AVG Variance % — Print jobs by qty band</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Job Type</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Qty Band</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>10% cut</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>15% cut</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>20% cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Print + Cut</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>1-49</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>27</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0.4749137041618482</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0.3274223337456634</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0.253676648537571</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0.1799309633294786</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000-4999</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0.01290478026161582</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.01290478026161582</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.01290478026161582</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0.01290478026161582</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Print + Cut</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>37</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0.1562566818722815</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.1562566818722815</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0.1562566818722815</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0.1562566818722815</v>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Impact vs Current (sample-level)</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Print + Cut</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>200-999</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>55</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>0.2090815015308145</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>0.08817335137773306</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0.02771927630119228</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>-0.03273479877534836</v>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Print rows in cut bands</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Total SPOT $ (baseline)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Total SPOT $ (scenario)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Δ vs iQuote before</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Δ vs iQuote after</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Revenue give-back</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Print + Cut</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>19</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0.01290478026161582</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.01290478026161582</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>0.01290478026161582</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>0.01290478026161582</v>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>82</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>169871.4399999999</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>169871.4399999999</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>27652.70999999993</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>27652.70999999993</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>1-49</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>42</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0.3526671949910359</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0.2174004754919323</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.1497671157423805</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>0.08213375599282877</v>
+          <t>10% cut</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>82</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>169871.4399999999</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>152884.296</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>27652.70999999993</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>10665.56600000002</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>-16987.14399999991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>23</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0.2061314167753698</v>
+          <t>15% cut</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>82</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>169871.4399999999</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>144390.724</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>27652.70999999993</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>2171.993999999977</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>-25480.71599999996</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>200-999</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>44</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>0.160664116803186</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.04459770512286743</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>-0.01343550071729191</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>-0.07146870655745115</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>15</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5000+</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Impact vs Current (sample-level)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Print rows in cut bands</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Total SPOT $ (baseline)</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Total SPOT $ (scenario)</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Δ vs iQuote before</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Δ vs iQuote after</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Revenue give-back</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>168</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>437542.69</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>437542.69</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>61709.55999999994</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>61709.55999999994</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10% cut</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>168</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>437542.69</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>393788.4210000001</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>61709.55999999994</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>17955.29100000003</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>-43754.26899999991</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>15% cut</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>168</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>437542.69</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>371911.2865</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>61709.55999999994</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>-3921.843500000075</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>-65631.40350000001</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
           <t>20% cut</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>168</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>437542.69</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>350034.152</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>61709.55999999994</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>-25798.97800000006</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>-87508.538</v>
+      <c r="B25" t="n">
+        <v>82</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>169871.4399999999</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>135897.152</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>27652.70999999993</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>-6321.578000000038</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>-33974.28799999997</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +1636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2677,115 +1761,6 @@
       </c>
       <c r="B10" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Qty Band</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Avg Variance %</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Median Variance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1-49</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0.3526671949910359</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0.2824245128794613</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>200-999</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>44</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>0.160664116803186</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0.1344094722554383</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5000+</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>-0.2663159846685904</v>
       </c>
     </row>
   </sheetData>
@@ -2800,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2925,115 +1900,6 @@
       </c>
       <c r="B10" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Qty Band</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Avg Variance %</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Median Variance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>1-49  (cut 10%)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0.2174004754919323</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0.1541820615915152</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>200-999  (cut 10%)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>0.04459770512286743</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>0.02096852502989452</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5000+</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>-0.2663159846685904</v>
       </c>
     </row>
   </sheetData>
@@ -3048,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3173,115 +2039,6 @@
       </c>
       <c r="B10" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Qty Band</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Avg Variance %</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Median Variance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>1-49  (cut 15%)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.1497671157423805</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.09006083594754205</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>200-999  (cut 15%)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>-0.01343550071729191</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>-0.03575194858287743</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5000+</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>-0.2663159846685904</v>
       </c>
     </row>
   </sheetData>
@@ -3296,7 +2053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3421,115 +2178,6 @@
       </c>
       <c r="B10" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Print + Cut + Finishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Qty Band</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Avg Variance %</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Median Variance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>1-49  (cut 20%)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.08213375599282877</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>0.02593961030356908</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>50-199</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.2061314167753698</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.149442747595529</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>200-999  (cut 20%)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>-0.07146870655745115</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>-0.0924724221956493</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1000-4999</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>-0.04253773864726</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0.007048749911299275</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5000+</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-0.2668606553161489</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>-0.2663159846685904</v>
       </c>
     </row>
   </sheetData>
@@ -3544,7 +2192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3561,7 +2209,7 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>WHAT IT SHOWS</t>
         </is>
@@ -3570,230 +2218,303 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The 10/15/20% print-price cut is applied to Print + Cut and Print + Cut + Finishing</t>
+          <t xml:space="preserve">  • Focused analysis on Print + Cut ONLY — Print + Cut + Finishing is</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    components in the 1-49 and 200-999 qty bands ONLY.</t>
+          <t xml:space="preserve">    EXCLUDED because finishing rates (Strip / Glue / Tape) are still</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • All other bands (50-199, 1000-4999, 5000+) are unchanged.</t>
+          <t xml:space="preserve">    uncalibrated placeholders in the SPOT engine and mask the true print</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Cut Only components are unchanged — this is a print-only scenario.</t>
+          <t xml:space="preserve">    pricing signal.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The 10/15/20% price cut is applied to Print + Cut components in the</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1-49 and 200-999 qty bands ONLY. Other bands unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>BASELINE NOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This tab uses the CORRECTED v3 join. The screenshot you were reviewing showed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  v2 numbers with a join bug (e.g., Print+Cut 200-999 Avg showed 85.88% because</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  a Shelf@1000 was mis-paired with a Header@1000). The corrected baseline has</t>
+          <t xml:space="preserve">  This tab uses the CORRECTED v3 join. The screenshot you were reviewing showed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  v2 numbers with a join bug (e.g., Print+Cut 200-999 Avg showed 85.88% because</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a Shelf@1000 was mis-paired with a Header@1000). The corrected baseline has</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Avg +20.91% for that cell.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>HOW TO USE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Compare 'Scenario Comparison' tab for the side-by-side matrix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Drill into each 'Scenario Nn%' tab for full tables + charts.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t xml:space="preserve">  1. Compare 'Scenario Comparison' tab for the side-by-side matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Drill into each 'Scenario Nn%' tab for full tables + charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">  3. Read the Revenue-Impact table at the bottom of 'Scenario Comparison'.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>WHAT THE 3 SCENARIOS DO TO EACH BAND</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1-49:</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 10% cut → Print + Cut median moves +31% → +18% (still elevated).</t>
+          <t>WHAT THE 3 SCENARIOS DO TO EACH BAND (Print + Cut only)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 15% cut → +31% → +12% (getting closer).</t>
+          <t xml:space="preserve">  1-49:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 20% cut → +31% → +5%  (near parity).</t>
+          <t xml:space="preserve">    • 10% cut → median +31% → +18% (still elevated)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  200-999:</t>
+          <t xml:space="preserve">    • 15% cut → +31% → +12% (getting closer)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 10% cut → Print + Cut median +24% → +11% (near parity).</t>
+          <t xml:space="preserve">    • 20% cut → +31% → +5%  (near parity)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 15% cut → +24% → +5%  (parity).</t>
+          <t xml:space="preserve">  200-999:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 20% cut → +24% → -1%  (slight underprice).</t>
+          <t xml:space="preserve">    • 10% cut → median +24% → +11% (near parity)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 15% cut → +24% → +5%  (parity)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>OBSERVED PATTERN</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 20% cut → +24% → -1%  (slight underprice)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • The 1-49 band starts wider (+31% median) than 200-999 (+24%).</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Same-% cut has different effect: 20% brings 1-49 to parity but pushes</t>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>WHY FINISHING WAS EXCLUDED</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    200-999 slightly UNDER iQuote.</t>
+          <t xml:space="preserve">  Print + Cut + Finishing rates for Strip, Glue and Tape are set from admin</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • If your goal is BOTH bands at parity, the honest answer is to split the</t>
+          <t xml:space="preserve">  placeholders that were never calibrated to actual/iQuote costs (see the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    lever: 20% in 1-49 and 10% in 200-999 (see prior analysis).</t>
+          <t xml:space="preserve">  amber '⚠ Placeholder' badges in Admin → Rates). Because SPOT under-charges</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  for finishing labor by an unknown amount, including P+C+F would show</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>NOTE ON 5000+ BAND</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  artificially closer variance to iQuote and could push those cells to below</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Intentionally excluded from this what-if. Only 3 data points, all from one</t>
+          <t xml:space="preserve">  parity with an aggressive print cut — that would be a false negative.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Model the print lever cleanly first; treat finishing as a separate exercise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OBSERVED PATTERN (Print + Cut only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 1-49 band starts wider (+31% median) than 200-999 (+24%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Same-% cut has different effect: 20% brings 1-49 to parity but pushes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    200-999 slightly UNDER iQuote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • If your goal is BOTH bands at parity, split the lever: 20% in 1-49 and</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    10% in 200-999 (see prior analysis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>NOTE ON 5000+ BAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Intentionally excluded from this what-if. Only 3 data points, all from one</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">  quote (Q224297 Die Cut Hand Formed). Decision deferred pending more data.</t>
         </is>

--- a/analysis/SPOT_Print_WhatIf_Scenarios.xlsx
+++ b/analysis/SPOT_Print_WhatIf_Scenarios.xlsx
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,10 +118,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1166,14 +1166,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Print Pricing — Scenario Comparison</t>
+          <t>Print Pricing — Scenario Comparison (Proofs Excluded)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Shading: green = within ±8% (near parity)  •  yellow = +overprice  •  red = -underprice  •  blue = qty band where cut applied</t>
+          <t>Shading: green = within ±8% (near parity)  •  yellow = +overprice  •  red = -underprice  •  blue = qty band where cut applied  •  qty=1 proof rows are EXCLUDED</t>
         </is>
       </c>
     </row>
@@ -1233,19 +1233,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.3133450911228687</v>
+        <v>0.621566401816118</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.1820105820105818</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.1163433274544385</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0.05067607289829511</v>
+        <v>0.4594097616345063</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.3783314415437003</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2972531214528943</v>
       </c>
     </row>
     <row r="7">
@@ -1385,19 +1385,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.4749137041618482</v>
+        <v>0.5887955408966281</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.3274223337456634</v>
+        <v>0.4299159868069654</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.253676648537571</v>
+        <v>0.3504762097621339</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.1799309633294786</v>
+        <v>0.2710364327173025</v>
       </c>
     </row>
     <row r="15">
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>169871.4399999999</v>
+        <v>164510.0599999999</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>169871.4399999999</v>
+        <v>164510.0599999999</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>27652.70999999993</v>
+        <v>26280.94999999992</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>27652.70999999993</v>
+        <v>26280.94999999992</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>0</v>
@@ -1557,22 +1557,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>169871.4399999999</v>
+        <v>164510.0599999999</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>152884.296</v>
+        <v>148059.054</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>27652.70999999993</v>
+        <v>26280.94999999992</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>10665.56600000002</v>
+        <v>9829.944000000018</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>-16987.14399999991</v>
+        <v>-16451.00599999991</v>
       </c>
     </row>
     <row r="24">
@@ -1582,22 +1582,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>169871.4399999999</v>
+        <v>164510.0599999999</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>144390.724</v>
+        <v>139833.551</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>27652.70999999993</v>
+        <v>26280.94999999992</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2171.993999999977</v>
+        <v>1604.440999999992</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>-25480.71599999996</v>
+        <v>-24676.50899999993</v>
       </c>
     </row>
     <row r="25">
@@ -1607,22 +1607,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>169871.4399999999</v>
+        <v>164510.0599999999</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>135897.152</v>
+        <v>131608.048</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>27652.70999999993</v>
+        <v>26280.94999999992</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>-6321.578000000038</v>
+        <v>-6621.062000000034</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>-33974.28799999997</v>
+        <v>-32902.01199999996</v>
       </c>
     </row>
   </sheetData>
@@ -1649,7 +1649,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SPOT Print Pricing — Variance by Qty Band</t>
+          <t>SPOT Print Pricing — Variance by Qty Band (Proofs Excluded)</t>
         </is>
       </c>
     </row>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4749137041618482</v>
+        <v>0.5887955408966281</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.3133450911228687</v>
+        <v>0.621566401816118</v>
       </c>
     </row>
     <row r="7">
@@ -1788,7 +1788,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SPOT Print Pricing — Variance by Qty Band</t>
+          <t>SPOT Print Pricing — Variance by Qty Band (Proofs Excluded)</t>
         </is>
       </c>
     </row>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.3274223337456634</v>
+        <v>0.4299159868069654</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1820105820105818</v>
+        <v>0.4594097616345063</v>
       </c>
     </row>
     <row r="7">
@@ -1927,7 +1927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SPOT Print Pricing — Variance by Qty Band</t>
+          <t>SPOT Print Pricing — Variance by Qty Band (Proofs Excluded)</t>
         </is>
       </c>
     </row>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.253676648537571</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0.1163433274544385</v>
+        <v>0.3504762097621339</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.3783314415437003</v>
       </c>
     </row>
     <row r="7">
@@ -2066,7 +2066,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SPOT Print Pricing — Variance by Qty Band</t>
+          <t>SPOT Print Pricing — Variance by Qty Band (Proofs Excluded)</t>
         </is>
       </c>
     </row>
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.1799309633294786</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0.05067607289829511</v>
+        <v>0.2710364327173025</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.2972531214528943</v>
       </c>
     </row>
     <row r="7">
@@ -2192,7 +2192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2246,275 +2246,303 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • The 10/15/20% price cut is applied to Print + Cut components in the</t>
+          <t xml:space="preserve">  • QTY = 1 PROOF ROWS ALSO EXCLUDED — the 1-49 band contained 14 qty=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1-49 and 200-999 qty bands ONLY. Other bands unchanged.</t>
+          <t xml:space="preserve">    rows (12 from a single quote Q224227 versioned proofs). These flat-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    setup proof charges distort the small-run signal. This tab shows the</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>BASELINE NOTE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'real production' 1-49 band = qty 2 through 49 only.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  This tab uses the CORRECTED v3 join. The screenshot you were reviewing showed</t>
+          <t xml:space="preserve">  • The 10/15/20% price cut is applied to Print + Cut components in the</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">    1-49 and 200-999 qty bands ONLY. Other bands unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>BASELINE NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This tab uses the CORRECTED v3 join. The screenshot you were reviewing showed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">  v2 numbers with a join bug (e.g., Print+Cut 200-999 Avg showed 85.88% because</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a Shelf@1000 was mis-paired with a Header@1000). The corrected baseline has</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Avg +20.91% for that cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>HOW TO USE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Compare 'Scenario Comparison' tab for the side-by-side matrix.</t>
+          <t xml:space="preserve">  a Shelf@1000 was mis-paired with a Header@1000). The corrected baseline has</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Drill into each 'Scenario Nn%' tab for full tables + charts.</t>
+          <t xml:space="preserve">  Avg +20.91% for that cell.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Read the Revenue-Impact table at the bottom of 'Scenario Comparison'.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>HOW TO USE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WHAT THE 3 SCENARIOS DO TO EACH BAND (Print + Cut only)</t>
+          <t xml:space="preserve">  1. Compare 'Scenario Comparison' tab for the side-by-side matrix.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1-49:</t>
+          <t xml:space="preserve">  2. Drill into each 'Scenario Nn%' tab for full tables + charts.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 10% cut → median +31% → +18% (still elevated)</t>
+          <t xml:space="preserve">  3. Read the Revenue-Impact table at the bottom of 'Scenario Comparison'.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • 15% cut → +31% → +12% (getting closer)</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 20% cut → +31% → +5%  (near parity)</t>
+          <t>WHAT THE 3 SCENARIOS DO TO EACH BAND (Print + Cut only)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  200-999:</t>
+          <t xml:space="preserve">  1-49:</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 10% cut → median +24% → +11% (near parity)</t>
+          <t xml:space="preserve">    • 10% cut → median +31% → +18% (still elevated)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 15% cut → +24% → +5%  (parity)</t>
+          <t xml:space="preserve">    • 15% cut → +31% → +12% (getting closer)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • 20% cut → +24% → -1%  (slight underprice)</t>
+          <t xml:space="preserve">    • 20% cut → +31% → +5%  (near parity)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  200-999:</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>WHY FINISHING WAS EXCLUDED</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    • 10% cut → median +24% → +11% (near parity)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Print + Cut + Finishing rates for Strip, Glue and Tape are set from admin</t>
+          <t xml:space="preserve">    • 15% cut → +24% → +5%  (parity)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  placeholders that were never calibrated to actual/iQuote costs (see the</t>
+          <t xml:space="preserve">    • 20% cut → +24% → -1%  (slight underprice)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  amber '⚠ Placeholder' badges in Admin → Rates). Because SPOT under-charges</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  for finishing labor by an unknown amount, including P+C+F would show</t>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>WHY FINISHING WAS EXCLUDED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  artificially closer variance to iQuote and could push those cells to below</t>
+          <t xml:space="preserve">  Print + Cut + Finishing rates for Strip, Glue and Tape are set from admin</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  parity with an aggressive print cut — that would be a false negative.</t>
+          <t xml:space="preserve">  placeholders that were never calibrated to actual/iQuote costs (see the</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Model the print lever cleanly first; treat finishing as a separate exercise.</t>
+          <t xml:space="preserve">  amber '⚠ Placeholder' badges in Admin → Rates). Because SPOT under-charges</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  for finishing labor by an unknown amount, including P+C+F would show</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OBSERVED PATTERN (Print + Cut only)</t>
+          <t xml:space="preserve">  artificially closer variance to iQuote and could push those cells to below</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • 1-49 band starts wider (+31% median) than 200-999 (+24%).</t>
+          <t xml:space="preserve">  parity with an aggressive print cut — that would be a false negative.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Same-% cut has different effect: 20% brings 1-49 to parity but pushes</t>
+          <t xml:space="preserve">  Model the print lever cleanly first; treat finishing as a separate exercise.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    200-999 slightly UNDER iQuote.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • If your goal is BOTH bands at parity, split the lever: 20% in 1-49 and</t>
+          <t>OBSERVED PATTERN (Print + Cut only)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10% in 200-999 (see prior analysis).</t>
+          <t xml:space="preserve">  • 1-49 band starts wider (+31% median) than 200-999 (+24%).</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Same-% cut has different effect: 20% brings 1-49 to parity but pushes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>NOTE ON 5000+ BAND</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    200-999 slightly UNDER iQuote.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Intentionally excluded from this what-if. Only 3 data points, all from one</t>
+          <t xml:space="preserve">  • If your goal is BOTH bands at parity, split the lever: 20% in 1-49 and</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    10% in 200-999 (see prior analysis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>NOTE ON 5000+ BAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Intentionally excluded from this what-if. Only 3 data points, all from one</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t xml:space="preserve">  quote (Q224297 Die Cut Hand Formed). Decision deferred pending more data.</t>
         </is>
